--- a/taxontabletools2/user_preferences.xlsx
+++ b/taxontabletools2/user_preferences.xlsx
@@ -1,43 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmacher/Documents/GitHub/TaxonTableTools2/taxontabletools2/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FEC2F2-4CD4-394D-B418-84463EBADF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>TTT_input_path_to_projects</t>
+  </si>
+  <si>
+    <t>TTT_height</t>
+  </si>
+  <si>
+    <t>TTT_width</t>
+  </si>
+  <si>
+    <t>TTT_showlegend</t>
+  </si>
+  <si>
+    <t>TTT_template</t>
+  </si>
+  <si>
+    <t>TTT_fontsize</t>
+  </si>
+  <si>
+    <t>TTT_hash</t>
+  </si>
+  <si>
+    <t>ESVs</t>
+  </si>
+  <si>
+    <t>TTT_scattersize</t>
+  </si>
+  <si>
+    <t>TTT_jitter</t>
+  </si>
+  <si>
+    <t>TTT_color1</t>
+  </si>
+  <si>
+    <t>TTT_color2</t>
+  </si>
+  <si>
+    <t>TTT_color3</t>
+  </si>
+  <si>
+    <t>TTT_colorsequence</t>
+  </si>
+  <si>
+    <t>Dark24</t>
+  </si>
+  <si>
+    <t>TTT_colorscale</t>
+  </si>
+  <si>
+    <t>viridis</t>
+  </si>
+  <si>
+    <t>navy</t>
+  </si>
+  <si>
+    <t>teal</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>simple_white</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +128,32 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,166 +441,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>project_name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>path_to_outdirs</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>/Users/tillmacher/Desktop/TTT_projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>plot_height</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>plot_width</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>show_legend</t>
-        </is>
-      </c>
-      <c r="B6" t="b">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>template</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>simple_white</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>font_size</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>clustering_unit</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ESVs</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>scatter_size</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>color_1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>navy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>color_2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>teal</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>colorsequence</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Plotly</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>colorscale</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>blues</t>
-        </is>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/taxontabletools2/user_preferences.xlsx
+++ b/taxontabletools2/user_preferences.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmacher/Documents/GitHub/TaxonTableTools2/taxontabletools2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FEC2F2-4CD4-394D-B418-84463EBADF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFB8BDE-29A1-A349-9B81-8D0E9A9B49F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Variable</t>
   </si>
@@ -43,6 +43,9 @@
     <t>TTT_template</t>
   </si>
   <si>
+    <t>TaxonTableTools</t>
+  </si>
+  <si>
     <t>TTT_fontsize</t>
   </si>
   <si>
@@ -55,18 +58,27 @@
     <t>TTT_scattersize</t>
   </si>
   <si>
+    <t>TTT_linewidth</t>
+  </si>
+  <si>
     <t>TTT_jitter</t>
   </si>
   <si>
     <t>TTT_color1</t>
   </si>
   <si>
+    <t>navy</t>
+  </si>
+  <si>
     <t>TTT_color2</t>
   </si>
   <si>
     <t>TTT_color3</t>
   </si>
   <si>
+    <t>orange</t>
+  </si>
+  <si>
     <t>TTT_colorsequence</t>
   </si>
   <si>
@@ -76,19 +88,10 @@
     <t>TTT_colorscale</t>
   </si>
   <si>
+    <t>teal</t>
+  </si>
+  <si>
     <t>viridis</t>
-  </si>
-  <si>
-    <t>navy</t>
-  </si>
-  <si>
-    <t>teal</t>
-  </si>
-  <si>
-    <t>orange</t>
-  </si>
-  <si>
-    <t>simple_white</t>
   </si>
 </sst>
 </file>
@@ -106,10 +109,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -120,12 +120,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -134,10 +149,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -442,129 +457,137 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="22.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>800</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="b">
-        <v>0</v>
+      <c r="B5" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
+      <c r="B16" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
